--- a/DATA/MODELADO/Diagnosticos/Exp01/diagnostico_modelo_Exp01.xlsx
+++ b/DATA/MODELADO/Diagnosticos/Exp01/diagnostico_modelo_Exp01.xlsx
@@ -555,12 +555,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MODELO NO APTO PARA DETECTAR OBJETIVO</t>
+          <t>Bueno</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Crítico</t>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
